--- a/listini-c75s/PF2_SENZA_VETRO.xlsx
+++ b/listini-c75s/PF2_SENZA_VETRO.xlsx
@@ -526,47 +526,47 @@
         <v>1900</v>
       </c>
       <c r="B3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -575,47 +575,47 @@
         <v>2000</v>
       </c>
       <c r="B4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -624,47 +624,47 @@
         <v>2100</v>
       </c>
       <c r="B5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -673,47 +673,47 @@
         <v>2200</v>
       </c>
       <c r="B6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -722,47 +722,47 @@
         <v>2300</v>
       </c>
       <c r="B7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -771,47 +771,47 @@
         <v>2400</v>
       </c>
       <c r="B8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -820,47 +820,47 @@
         <v>2500</v>
       </c>
       <c r="B9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -869,47 +869,47 @@
         <v>2600</v>
       </c>
       <c r="B10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -918,47 +918,47 @@
         <v>2700</v>
       </c>
       <c r="B11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1014,47 +1014,47 @@
         <v>1900</v>
       </c>
       <c r="B16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L16" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1063,47 +1063,47 @@
         <v>2000</v>
       </c>
       <c r="B17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L17" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1112,47 +1112,47 @@
         <v>2100</v>
       </c>
       <c r="B18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L18" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1161,47 +1161,47 @@
         <v>2200</v>
       </c>
       <c r="B19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L19" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A19)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A19)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1210,47 +1210,47 @@
         <v>2300</v>
       </c>
       <c r="B20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L20" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A20)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A20)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1259,47 +1259,47 @@
         <v>2400</v>
       </c>
       <c r="B21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L21" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A21)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A21)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1308,47 +1308,47 @@
         <v>2500</v>
       </c>
       <c r="B22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L22" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A22)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A22)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1357,47 +1357,47 @@
         <v>2600</v>
       </c>
       <c r="B23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1406,47 +1406,47 @@
         <v>2700</v>
       </c>
       <c r="B24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1461,84 +1461,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Prezzo profili €/kg (10820 CAT.B +ADD — RAL 7016)</t>
+          <t>Prezzo profili taglio termico €/kg (33320 CAT.B +ADD — RAL 7016)</t>
         </is>
       </c>
       <c r="B1" s="6" t="n">
-        <v>14.82</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Sconto profili su listino AluK</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>0.43</v>
+          <t>Prezzo profili normali €/kg (10820 CAT.B +ADD — fermavetri, aggiuntivi, gocciolatoio)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>14.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Sconto accessori/guarnizioni su listino AluK</t>
+          <t>Sconto profili su listino AluK C75S/C82S-CS</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Sfrido</t>
+          <t>Sconto accessori/guarnizioni su listino AluK</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Tariffa oraria manodopera €/h</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>65</v>
+          <t>Sfrido</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Tariffa oraria manodopera €/h</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Ricarico su costo totale</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B7" s="7" t="n">
         <v>2.13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Celle gialle = valori modificabili: tutte le griglie si ricalcolano.</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Listino AluK decorrenza 15-06-2026. Ferramenta: prezzi nel foglio dedicato.</t>
+          <t>Celle gialle = valori modificabili: tutte le griglie si ricalcolano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Prezzi: listino AluK C75S/C82S-CS decorrenza 2026-06-15 (listini-db). Ferramenta: prezzi nel foglio dedicato.</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1562,122 +1572,159 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Peso alluminio costante (kg)</t>
+          <t>Peso profili taglio termico costante (kg)</t>
         </is>
       </c>
       <c r="B1" s="5" t="n">
-        <v>-0.78388</v>
+        <v>-0.33316</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Peso per mm di L (kg/mm)</t>
+          <t>Peso taglio termico per mm di L (kg/mm)</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.00655</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Peso per mm di H (kg/mm)</t>
+          <t>Peso taglio termico per mm di H (kg/mm)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.01087</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Guarnizioni costante (€ listino)</t>
+          <t>Peso profili normali costante (kg)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.015277</v>
+        <v>-0.45072</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Guarnizioni per mm di L (€/mm)</t>
+          <t>Peso normali per mm di L (kg/mm)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.003944</v>
+        <v>0.00095</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Guarnizioni per mm di H (€/mm)</t>
+          <t>Peso normali per mm di H (kg/mm)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.003157</v>
+        <v>0.00187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Accessori totale (€ listino)</t>
+          <t>Guarnizioni costante (€ listino)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>51.502</v>
+        <v>0.015277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ore manodopera</t>
+          <t>Guarnizioni per mm di L (€/mm)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4.33333333</v>
+        <v>0.003944</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Guarnizioni per mm di H (€/mm)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0.003157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Derivati dalle distinte catalogo AluK C75S sez. 8 e pesi kg/m catalogo v3.</t>
-        </is>
+          <t>Accessori totale (€ listino)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>51.502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Assunzioni: supporti vetro V62008 = 4 per vetro; mascherine V51015 = 2 pz;</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>fermavetro battenti N45860 (0,37 kg/m), fisso coppia N45856 (0,62 kg/m);</t>
-        </is>
+          <t>Ore manodopera</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4.33333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>squadrette V40022/V40037 prezzate come V40022 (0,607 €).</t>
+          <t>Derivati dalle distinte catalogo AluK C75S sez. 8 e pesi kg/m catalogo v3.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Manodopera: 1h telaio + 1h/anta + 20' ferramenta/anta + 20'/vetro.</t>
+          <t>Assunzioni: supporti vetro V62008 = 4 per vetro; mascherine V51015 = 2 pz;</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Prezzi unitari accessori e guarnizioni dal listino AluK 15-06-2026 (pre-sconto).</t>
+          <t>fermavetro battenti N45860 (0,37 kg/m), fisso coppia N45856 (0,62 kg/m);</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>squadrette V40022/V40037 prezzate come V40022 (0,607 €).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Manodopera: 1h telaio + 1h/anta + 20' ferramenta/anta + 20'/vetro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Taglio termico = codici B (stipite, anta, battuta centrale, soglia); normali = N/K (aggiuntivo, gocciolatoio, fermavetri).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Prezzi unitari accessori e guarnizioni (pre-sconto): listino AluK C75S/C82S-CS decorrenza 2026-06-15 (listini-db).</t>
         </is>
       </c>
     </row>
